--- a/outputs/Block2_National_Nested_Folds_v12.xlsx
+++ b/outputs/Block2_National_Nested_Folds_v12.xlsx
@@ -528,13 +528,13 @@
         <v>3.967840869181249</v>
       </c>
       <c r="G2">
-        <v>6.31964891769215</v>
+        <v>6.319648917692146</v>
       </c>
       <c r="H2">
-        <v>0.5024446975396468</v>
+        <v>0.5024446975396469</v>
       </c>
       <c r="I2">
-        <v>0.4975553024603532</v>
+        <v>0.497555302460353</v>
       </c>
       <c r="J2" t="s">
         <v>21</v>
@@ -660,13 +660,13 @@
         <v>5.114197416147853</v>
       </c>
       <c r="G5">
-        <v>6.296610326132402</v>
+        <v>6.2966103261324</v>
       </c>
       <c r="H5">
-        <v>0.5542790760933821</v>
+        <v>0.5542790760933822</v>
       </c>
       <c r="I5">
-        <v>0.4457209239066179</v>
+        <v>0.4457209239066178</v>
       </c>
       <c r="J5" t="s">
         <v>21</v>
@@ -792,13 +792,13 @@
         <v>3.69459999331273</v>
       </c>
       <c r="G8">
-        <v>6.282988749273807</v>
+        <v>6.282988749273805</v>
       </c>
       <c r="H8">
-        <v>0.5705583655149382</v>
+        <v>0.5705583655149384</v>
       </c>
       <c r="I8">
-        <v>0.4294416344850617</v>
+        <v>0.4294416344850616</v>
       </c>
       <c r="J8" t="s">
         <v>21</v>
@@ -924,10 +924,10 @@
         <v>4.139788819212143</v>
       </c>
       <c r="G11">
-        <v>5.291968212462604</v>
+        <v>5.291968212462608</v>
       </c>
       <c r="H11">
-        <v>0.5074764797709386</v>
+        <v>0.5074764797709387</v>
       </c>
       <c r="I11">
         <v>0.4925235202290613</v>
@@ -1056,13 +1056,13 @@
         <v>3.753336425842188</v>
       </c>
       <c r="G14">
-        <v>6.661208146972516</v>
+        <v>6.661208146972521</v>
       </c>
       <c r="H14">
-        <v>0.5677908010583421</v>
+        <v>0.5677908010583419</v>
       </c>
       <c r="I14">
-        <v>0.4322091989416579</v>
+        <v>0.4322091989416581</v>
       </c>
       <c r="J14" t="s">
         <v>21</v>
